--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104705_W28.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104705_W28.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.1706</v>
+        <v>9.081200000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>8.7233</v>
+        <v>8.453099999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4472</v>
+        <v>0.6281</v>
       </c>
       <c r="G2" t="n">
-        <v>5.6411</v>
+        <v>5.6306</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.6783</v>
+        <v>-1.6692</v>
       </c>
       <c r="I2" t="n">
-        <v>7.3194</v>
+        <v>7.2997</v>
       </c>
       <c r="J2" t="n">
-        <v>8.083500000000001</v>
+        <v>8.037699999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.1181</v>
+        <v>-0.1314</v>
       </c>
       <c r="L2" t="n">
-        <v>8.201599999999999</v>
+        <v>8.1691</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.4424</v>
+        <v>-2.4072</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.5602</v>
+        <v>-1.5378</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.8822</v>
+        <v>-0.8694</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="R2" t="n">
-        <v>3.4025</v>
+        <v>3.4145</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9243</v>
+        <v>0.8384</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0424</v>
+        <v>-0.1701</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8819</v>
+        <v>1.0085</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7905</v>
+        <v>0.7912</v>
       </c>
       <c r="W2" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.3948</v>
+        <v>-1.3877</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.9514</v>
+        <v>8.470599999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>8.0718</v>
+        <v>8.2707</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1204</v>
+        <v>0.1999</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3305</v>
+        <v>0.3247</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.909</v>
+        <v>-0.9131</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2395</v>
+        <v>1.2378</v>
       </c>
       <c r="J3" t="n">
-        <v>3.0079</v>
+        <v>2.9755</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0999</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>2.908</v>
+        <v>2.8968</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.6774</v>
+        <v>-2.6508</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.0089</v>
+        <v>-0.9918</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.6685</v>
+        <v>-1.659</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8405</v>
+        <v>-0.3031</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9043</v>
+        <v>-0.6483</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0638</v>
+        <v>0.3452</v>
       </c>
       <c r="V3" t="n">
-        <v>7.3272</v>
+        <v>7.3108</v>
       </c>
       <c r="W3" t="n">
-        <v>7.1024</v>
+        <v>7.0816</v>
       </c>
       <c r="X3" t="n">
-        <v>0.2249</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="4">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1397</v>
+        <v>0.7681</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.591</v>
+        <v>-0.0092</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7307</v>
+        <v>0.7773</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2031</v>
+        <v>0.2119</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.7778</v>
+        <v>-0.7729</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9809</v>
+        <v>0.9848</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6607</v>
+        <v>0.6578000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6234</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4576</v>
+        <v>-0.4458</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.4012</v>
+        <v>-1.3934</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9436</v>
+        <v>0.9476</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0027</v>
+        <v>0.626</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2782</v>
+        <v>0.3134</v>
       </c>
       <c r="U4" t="n">
-        <v>0.281</v>
+        <v>0.3126</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. PELOS</t>
+          <t>A. ALBICY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.6914</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0335</v>
+        <v>0.5193</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.9447</v>
+        <v>0.1722</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2159</v>
+        <v>-0.8633999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>0.08799999999999999</v>
+        <v>-1.9137</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3039</v>
+        <v>1.0503</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6516</v>
+        <v>2.074</v>
       </c>
       <c r="K5" t="n">
-        <v>0.876</v>
+        <v>-0.376</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7755</v>
+        <v>2.45</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.8675</v>
+        <v>-2.9375</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.788</v>
+        <v>-1.5378</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.0795</v>
+        <v>-1.3997</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9073</v>
+        <v>1.1382</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="R5" t="n">
-        <v>2.4952</v>
+        <v>2.7316</v>
       </c>
       <c r="S5" t="n">
-        <v>1.7242</v>
+        <v>0.3995</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8771</v>
+        <v>-0.2769</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8471</v>
+        <v>0.6763</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.3267</v>
+        <v>0.0173</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0927</v>
+        <v>0.3155</v>
       </c>
       <c r="X5" t="n">
-        <v>-3.4194</v>
+        <v>-0.2983</v>
       </c>
     </row>
     <row r="6">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0241</v>
+        <v>0.1246</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2368</v>
+        <v>0.3486</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2609</v>
+        <v>-0.224</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.5218</v>
+        <v>-1.5212</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5195</v>
+        <v>-0.5171</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.0023</v>
+        <v>-1.0041</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7354000000000001</v>
+        <v>-0.7315</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5195</v>
+        <v>-0.5171</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2159</v>
+        <v>-0.2144</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0487</v>
+        <v>0.101</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0696</v>
+        <v>0.0487</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0209</v>
+        <v>0.0523</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. ALBICY</t>
+          <t>L. MANIEMA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0275</v>
+        <v>-0.3718</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2877</v>
+        <v>0.0858</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3152</v>
+        <v>-0.4576</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.8834</v>
+        <v>-0.5075</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.9309</v>
+        <v>-0.1724</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0476</v>
+        <v>-0.3351</v>
       </c>
       <c r="J7" t="n">
-        <v>2.0894</v>
+        <v>0.0372</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.3708</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>2.4602</v>
+        <v>0.0372</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.9728</v>
+        <v>-0.5447</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.5602</v>
+        <v>-0.1724</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.4126</v>
+        <v>-0.3724</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1342</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.5878</v>
+        <v>-0.2276</v>
       </c>
       <c r="R7" t="n">
-        <v>2.722</v>
+        <v>0.2276</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2976</v>
+        <v>0.1184</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5353</v>
+        <v>0.1184</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2377</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0193</v>
+        <v>0.0173</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3214</v>
+        <v>0.1578</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3021</v>
+        <v>-0.1405</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. METU</t>
+          <t>C. ALOCEN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2935</v>
+        <v>-0.5727</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3563</v>
+        <v>-1.422</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0628</v>
+        <v>0.8493000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.2969</v>
+        <v>-1.8944</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.212</v>
+        <v>-1.4386</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.0849</v>
+        <v>-0.4558</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3241</v>
+        <v>-1.4498</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6518</v>
+        <v>-0.7347</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3277</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.9728</v>
+        <v>-0.4446</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.5602</v>
+        <v>-0.7039</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.4126</v>
+        <v>0.2593</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9073</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.6293</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>2.722</v>
+        <v>0.9105</v>
       </c>
       <c r="S8" t="n">
-        <v>1.7061</v>
+        <v>0.4599</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2511</v>
+        <v>0.0765</v>
       </c>
       <c r="U8" t="n">
-        <v>1.455</v>
+        <v>0.3834</v>
       </c>
       <c r="V8" t="n">
-        <v>2.2046</v>
+        <v>1.0895</v>
       </c>
       <c r="W8" t="n">
-        <v>2.3461</v>
+        <v>1.0895</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1414</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,37 +1111,37 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3983</v>
+        <v>-0.7518</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2944</v>
+        <v>-0.0623</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6927</v>
+        <v>-0.6895</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1846</v>
+        <v>-1.1861</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.1846</v>
+        <v>-1.1861</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.492</v>
+        <v>-0.4966</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.492</v>
+        <v>-0.4966</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6927</v>
+        <v>-0.6895</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6927</v>
+        <v>-0.6895</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1156,10 +1156,10 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7864</v>
+        <v>0.4343</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7864</v>
+        <v>0.4343</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. MANIEMA</t>
+          <t>P. PELOS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.4897</v>
+        <v>-0.8887</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0288</v>
+        <v>1.3614</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4609</v>
+        <v>-2.2501</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.509</v>
+        <v>-0.2243</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1732</v>
+        <v>0.089</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3359</v>
+        <v>-0.3132</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0373</v>
+        <v>1.6241</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>0.8651</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0373</v>
+        <v>0.759</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5463</v>
+        <v>-1.8483</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1732</v>
+        <v>-0.7761</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3732</v>
+        <v>-1.0722</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.9105</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.2268</v>
+        <v>-1.5934</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2268</v>
+        <v>2.5039</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>0.7444</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>0.2413</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>0.5032</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0193</v>
+        <v>-2.3194</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1607</v>
+        <v>1.0895</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1414</v>
+        <v>-3.4089</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C. ALOCEN</t>
+          <t>C. METU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.7306</v>
+        <v>-0.9836</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7557</v>
+        <v>-1.7492</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0251</v>
+        <v>0.7655999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.8886</v>
+        <v>-3.3018</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.4328</v>
+        <v>-2.2143</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4558</v>
+        <v>-1.0875</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.4359</v>
+        <v>-0.3643</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.7242</v>
+        <v>-0.6765</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7117</v>
+        <v>0.3121</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.4526</v>
+        <v>-2.9375</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7086</v>
+        <v>-1.5378</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2559</v>
+        <v>-1.3997</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.2268</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>-3.6421</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9073</v>
+        <v>2.7316</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2922</v>
+        <v>1.0325</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2782</v>
+        <v>-0.0795</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5704</v>
+        <v>1.112</v>
       </c>
       <c r="V11" t="n">
-        <v>1.0927</v>
+        <v>2.1962</v>
       </c>
       <c r="W11" t="n">
-        <v>1.0927</v>
+        <v>2.3367</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.1405</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. TOBEY</t>
+          <t>K. ROBERTSON</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.1622</v>
+        <v>-2.1719</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.8924</v>
+        <v>-3.8315</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2698</v>
+        <v>1.6596</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.3006</v>
+        <v>-1.8618</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.1891</v>
+        <v>-3.323</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.1115</v>
+        <v>1.4612</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.483</v>
+        <v>-1.3899</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0795</v>
+        <v>-2.231</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5625</v>
+        <v>0.8411</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.8176</v>
+        <v>-0.4719</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2685</v>
+        <v>-1.092</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.549</v>
+        <v>0.6201</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.6805</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.361</v>
+        <v>-2.5039</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6805</v>
+        <v>1.3658</v>
       </c>
       <c r="S12" t="n">
-        <v>0.9116</v>
+        <v>0.828</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0484</v>
+        <v>0.0624</v>
       </c>
       <c r="U12" t="n">
-        <v>0.9599</v>
+        <v>0.7655999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>K. ROBERTSON</t>
+          <t>M. TOBEY</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.0886</v>
+        <v>-2.5633</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.628</v>
+        <v>-2.1922</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5394</v>
+        <v>-0.3711</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.8598</v>
+        <v>-1.2949</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.3231</v>
+        <v>-0.1868</v>
       </c>
       <c r="I13" t="n">
-        <v>1.4634</v>
+        <v>-1.1081</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.3677</v>
+        <v>-0.494</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.2205</v>
+        <v>0.0722</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8529</v>
+        <v>-0.5662</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.4921</v>
+        <v>-0.8008999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.1026</v>
+        <v>-0.259</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6105</v>
+        <v>-0.5419</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.1342</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.4952</v>
+        <v>-1.3658</v>
       </c>
       <c r="R13" t="n">
-        <v>1.361</v>
+        <v>0.6829</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.09470000000000001</v>
+        <v>0.504</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7652</v>
+        <v>-0.3324</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6705</v>
+        <v>0.8364</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>10.1361</v>
+        <v>10.8321</v>
       </c>
       <c r="E14" t="n">
-        <v>9.395299999999994</v>
+        <v>9.772499999999997</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7405999999999999</v>
+        <v>1.0597</v>
       </c>
       <c r="G14" t="n">
-        <v>-6.485900000000001</v>
+        <v>-6.488199999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>-14.2423</v>
+        <v>-14.2182</v>
       </c>
       <c r="I14" t="n">
-        <v>7.756499999999999</v>
+        <v>7.729999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>10.6413</v>
+        <v>10.4221</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.8986</v>
+        <v>-3.0097</v>
       </c>
       <c r="L14" t="n">
-        <v>13.5399</v>
+        <v>13.4315</v>
       </c>
       <c r="M14" t="n">
-        <v>-17.1272</v>
+        <v>-16.9102</v>
       </c>
       <c r="N14" t="n">
-        <v>-11.3438</v>
+        <v>-11.2086</v>
       </c>
       <c r="O14" t="n">
-        <v>-5.783500000000001</v>
+        <v>-5.701700000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2685</v>
+        <v>2.2765</v>
       </c>
       <c r="Q14" t="n">
-        <v>-15.8783</v>
+        <v>-15.9342</v>
       </c>
       <c r="R14" t="n">
-        <v>18.1466</v>
+        <v>18.2105</v>
       </c>
       <c r="S14" t="n">
-        <v>5.065999999999999</v>
+        <v>5.783300000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9221999999999999</v>
+        <v>-0.2122</v>
       </c>
       <c r="U14" t="n">
-        <v>5.9882</v>
+        <v>5.995500000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>9.287599999999999</v>
+        <v>9.260700000000002</v>
       </c>
       <c r="W14" t="n">
-        <v>15.5547</v>
+        <v>15.4968</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.2669</v>
+        <v>-6.2362</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.0332</v>
+        <v>4.2878</v>
       </c>
       <c r="E15" t="n">
-        <v>5.7791</v>
+        <v>5.4012</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7459</v>
+        <v>-1.1134</v>
       </c>
       <c r="G15" t="n">
-        <v>2.3503</v>
+        <v>2.3605</v>
       </c>
       <c r="H15" t="n">
-        <v>2.7474</v>
+        <v>2.7458</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3971</v>
+        <v>-0.3853</v>
       </c>
       <c r="J15" t="n">
-        <v>4.8524</v>
+        <v>4.8349</v>
       </c>
       <c r="K15" t="n">
-        <v>2.8746</v>
+        <v>2.8613</v>
       </c>
       <c r="L15" t="n">
-        <v>1.9778</v>
+        <v>1.9736</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.502</v>
+        <v>-2.4744</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1272</v>
+        <v>-0.1155</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.3749</v>
+        <v>-2.3588</v>
       </c>
       <c r="P15" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0353</v>
+        <v>0.2753</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0998</v>
+        <v>-0.4533</v>
       </c>
       <c r="U15" t="n">
-        <v>1.135</v>
+        <v>0.7286</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.1671</v>
+        <v>-0.1691</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.4205</v>
+        <v>-1.4163</v>
       </c>
     </row>
     <row r="16">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9252</v>
+        <v>1.8227</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1473</v>
+        <v>0.1139</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7779</v>
+        <v>1.7089</v>
       </c>
       <c r="G16" t="n">
-        <v>1.1533</v>
+        <v>1.1535</v>
       </c>
       <c r="H16" t="n">
-        <v>1.7317</v>
+        <v>1.7237</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5784</v>
+        <v>-0.5702</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3845</v>
+        <v>1.3648</v>
       </c>
       <c r="K16" t="n">
-        <v>1.198</v>
+        <v>1.1786</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1866</v>
+        <v>0.1862</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2312</v>
+        <v>-0.2113</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5337</v>
+        <v>0.5451</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.7649</v>
+        <v>-0.7563</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1866</v>
+        <v>-0.2821</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6079</v>
+        <v>-0.6088</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4213</v>
+        <v>0.3267</v>
       </c>
       <c r="V16" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W16" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>K. BRUNOT</t>
+          <t>O. LIVINGSTON</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1573</v>
+        <v>0.4694</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>1.2343</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1573</v>
+        <v>-0.7649</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1573</v>
+        <v>4.0583</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1573</v>
+        <v>3.5652</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>0.4931</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>6.5747</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>3.3505</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>3.2243</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1573</v>
+        <v>-2.5164</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1573</v>
+        <v>0.2148</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>-2.7312</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-3.8697</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-5.9184</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.0487</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-0.324</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>-0.6692</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>0.3452</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.6049</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.6424</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. HILDRETH</t>
+          <t>K. BRUNOT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0171</v>
+        <v>0.1579</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0757</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0586</v>
+        <v>0.1579</v>
       </c>
       <c r="G18" t="n">
-        <v>1.6648</v>
+        <v>0.1579</v>
       </c>
       <c r="H18" t="n">
-        <v>3.3174</v>
+        <v>0.1579</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.6526</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1.7201</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>3.2555</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.5354</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0554</v>
+        <v>0.1579</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0619</v>
+        <v>0.1579</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1172</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9073</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2867</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4688</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1821</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O. LIVINGSTON</t>
+          <t>C. HILDRETH</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1414</v>
+        <v>-0.0598</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0725</v>
+        <v>0.0422</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2139</v>
+        <v>-0.102</v>
       </c>
       <c r="G19" t="n">
-        <v>4.0763</v>
+        <v>1.6567</v>
       </c>
       <c r="H19" t="n">
-        <v>3.5831</v>
+        <v>3.3118</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4931</v>
+        <v>-1.6551</v>
       </c>
       <c r="J19" t="n">
-        <v>6.621</v>
+        <v>1.6985</v>
       </c>
       <c r="K19" t="n">
-        <v>3.3799</v>
+        <v>3.2405</v>
       </c>
       <c r="L19" t="n">
-        <v>3.2411</v>
+        <v>-1.542</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.5447</v>
+        <v>-0.0417</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2033</v>
+        <v>0.0713</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.748</v>
+        <v>-0.113</v>
       </c>
       <c r="P19" t="n">
-        <v>-3.8562</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q19" t="n">
-        <v>-5.8976</v>
+        <v>-2.2763</v>
       </c>
       <c r="R19" t="n">
-        <v>2.0415</v>
+        <v>0.9105</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9657</v>
+        <v>-0.3507</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9043</v>
+        <v>-0.4694</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0614</v>
+        <v>0.1187</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6041</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2534</v>
+        <v>1.0895</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6492</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="20">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6348</v>
+        <v>-0.6235000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5717</v>
+        <v>-0.5841</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0631</v>
+        <v>-0.0393</v>
       </c>
       <c r="G20" t="n">
-        <v>0.039</v>
+        <v>0.0464</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3375</v>
+        <v>0.3443</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2985</v>
+        <v>-0.2979</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0543</v>
+        <v>0.0432</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.3534</v>
+        <v>-0.3587</v>
       </c>
       <c r="L20" t="n">
-        <v>0.4078</v>
+        <v>0.4019</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0153</v>
+        <v>0.0032</v>
       </c>
       <c r="N20" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.703</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7063</v>
+        <v>-0.6998</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8741</v>
+        <v>-0.8779</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6261</v>
+        <v>-0.6273</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.248</v>
+        <v>-0.2505</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="21">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0438</v>
+        <v>-1.146</v>
       </c>
       <c r="E21" t="n">
-        <v>1.491</v>
+        <v>1.6984</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.5348</v>
+        <v>-2.8443</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4485</v>
+        <v>0.4551</v>
       </c>
       <c r="H21" t="n">
-        <v>1.6826</v>
+        <v>1.6776</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.234</v>
+        <v>-1.2225</v>
       </c>
       <c r="J21" t="n">
-        <v>2.5029</v>
+        <v>2.4861</v>
       </c>
       <c r="K21" t="n">
-        <v>1.7938</v>
+        <v>1.7786</v>
       </c>
       <c r="L21" t="n">
-        <v>0.709</v>
+        <v>0.7075</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.0543</v>
+        <v>-2.031</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1113</v>
+        <v>-0.1011</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.9431</v>
+        <v>-1.93</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4594</v>
+        <v>-0.5702</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9043</v>
+        <v>-0.6692</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4449</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2598</v>
+        <v>-1.2586</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.5131</v>
+        <v>-2.5058</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G. FERRANDO</t>
+          <t>D. NEEDHAM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.466</v>
+        <v>-1.8739</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5231</v>
+        <v>-0.405</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9429</v>
+        <v>-1.469</v>
       </c>
       <c r="G22" t="n">
-        <v>0.7047</v>
+        <v>0.3203</v>
       </c>
       <c r="H22" t="n">
-        <v>1.5497</v>
+        <v>-0.0252</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.845</v>
+        <v>0.3454</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1803</v>
+        <v>2.3629</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6061</v>
+        <v>-0.5558</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7864</v>
+        <v>2.9187</v>
       </c>
       <c r="M22" t="n">
-        <v>0.885</v>
+        <v>-2.0426</v>
       </c>
       <c r="N22" t="n">
-        <v>0.9436</v>
+        <v>0.5306</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0586</v>
+        <v>-2.5733</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.4537</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-2.5039</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6805</v>
+        <v>2.2763</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5317</v>
+        <v>-0.9372</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2087</v>
+        <v>-0.8087</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.323</v>
+        <v>-0.1286</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.1853</v>
+        <v>-1.0293</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.1853</v>
+        <v>-1.5741</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. NEEDHAM</t>
+          <t>G. FERRANDO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.502</v>
+        <v>-2.5264</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.5829</v>
+        <v>-1.5336</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.919</v>
+        <v>-0.9927</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3364</v>
+        <v>0.7047</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.0128</v>
+        <v>1.5509</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3492</v>
+        <v>-0.8462</v>
       </c>
       <c r="J23" t="n">
-        <v>2.4093</v>
+        <v>-0.1864</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.5306</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>2.9399</v>
+        <v>-0.7896</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.0729</v>
+        <v>0.8911</v>
       </c>
       <c r="N23" t="n">
-        <v>0.5178</v>
+        <v>0.9476</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.5908</v>
+        <v>-0.0565</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.2268</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.4952</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>2.2683</v>
+        <v>0.6829</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.5766</v>
+        <v>-0.5969</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0434</v>
+        <v>-0.2091</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5332</v>
+        <v>-0.3878</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.0349</v>
+        <v>-2.1789</v>
       </c>
       <c r="W23" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.5812</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="24">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.2127</v>
+        <v>-3.0722</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.0229</v>
+        <v>-2.0315</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.1898</v>
+        <v>-1.0408</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.0231</v>
+        <v>-1.0142</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0591</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.0822</v>
+        <v>-1.0799</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.3969</v>
+        <v>-1.4042</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6478</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3737</v>
+        <v>0.39</v>
       </c>
       <c r="N24" t="n">
-        <v>0.7069</v>
+        <v>0.7174</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.3331</v>
+        <v>-0.3275</v>
       </c>
       <c r="P24" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1384</v>
+        <v>-1.0173</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6261</v>
+        <v>-0.6273</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5123</v>
+        <v>-0.3899</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>P. BUSQUETS</t>
+          <t>P. VILDOZA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.5831</v>
+        <v>-3.5189</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.9453</v>
+        <v>-1.6687</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.6378</v>
+        <v>-1.8502</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.6921</v>
+        <v>-1.728</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.6552</v>
+        <v>-0.2502</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.0369</v>
+        <v>-1.4779</v>
       </c>
       <c r="J25" t="n">
-        <v>0.4209</v>
+        <v>-1.269</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.5439000000000001</v>
+        <v>0.3103</v>
       </c>
       <c r="L25" t="n">
-        <v>0.9648</v>
+        <v>-1.5793</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.113</v>
+        <v>-0.459</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.1113</v>
+        <v>-0.5604</v>
       </c>
       <c r="O25" t="n">
-        <v>-2.0017</v>
+        <v>0.1014</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.2268</v>
+        <v>0.4553</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.4952</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.2683</v>
+        <v>0.4553</v>
       </c>
       <c r="S25" t="n">
-        <v>0.5275</v>
+        <v>-0.4542</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.0998</v>
+        <v>-0.3997</v>
       </c>
       <c r="U25" t="n">
-        <v>0.6273</v>
+        <v>-0.0545</v>
       </c>
       <c r="V25" t="n">
-        <v>-2.1917</v>
+        <v>-1.792</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.7712</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.4205</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>P. VILDOZA</t>
+          <t>P. BUSQUETS</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.685</v>
+        <v>-4.0522</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.6602</v>
+        <v>-3.3267</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.0248</v>
+        <v>-0.7255</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.7296</v>
+        <v>-1.6831</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.2555</v>
+        <v>-0.6494</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.4741</v>
+        <v>-1.0337</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.261</v>
+        <v>0.4045</v>
       </c>
       <c r="K26" t="n">
-        <v>0.3117</v>
+        <v>-0.5483</v>
       </c>
       <c r="L26" t="n">
-        <v>-1.5727</v>
+        <v>0.9528</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.4685</v>
+        <v>-2.0876</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.5672</v>
+        <v>-0.1011</v>
       </c>
       <c r="O26" t="n">
-        <v>0.09859999999999999</v>
+        <v>-1.9865</v>
       </c>
       <c r="P26" t="n">
-        <v>0.4537</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>-2.5039</v>
       </c>
       <c r="R26" t="n">
-        <v>0.4537</v>
+        <v>2.2763</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.6094000000000001</v>
+        <v>0.0487</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.3992</v>
+        <v>-0.4533</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.2102</v>
+        <v>0.5021</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.7997</v>
+        <v>-2.1903</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>-0.7739</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.7997</v>
+        <v>-1.4163</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-10.136</v>
+        <v>-10.1351</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.7404999999999997</v>
+        <v>-1.059599999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>-9.395399999999999</v>
+        <v>-9.0753</v>
       </c>
       <c r="G27" t="n">
-        <v>6.485799999999999</v>
+        <v>6.488100000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>14.2423</v>
+        <v>14.2181</v>
       </c>
       <c r="I27" t="n">
-        <v>-7.7565</v>
+        <v>-7.7302</v>
       </c>
       <c r="J27" t="n">
-        <v>17.12720000000001</v>
+        <v>16.91</v>
       </c>
       <c r="K27" t="n">
-        <v>11.3439</v>
+        <v>11.2086</v>
       </c>
       <c r="L27" t="n">
-        <v>5.7835</v>
+        <v>5.7017</v>
       </c>
       <c r="M27" t="n">
-        <v>-10.6413</v>
+        <v>-10.4218</v>
       </c>
       <c r="N27" t="n">
-        <v>2.8985</v>
+        <v>3.0096</v>
       </c>
       <c r="O27" t="n">
-        <v>-13.54</v>
+        <v>-13.4315</v>
       </c>
       <c r="P27" t="n">
-        <v>-2.2683</v>
+        <v>-2.2762</v>
       </c>
       <c r="Q27" t="n">
-        <v>-18.1466</v>
+        <v>-18.2104</v>
       </c>
       <c r="R27" t="n">
-        <v>15.8782</v>
+        <v>15.9342</v>
       </c>
       <c r="S27" t="n">
-        <v>-5.065799999999999</v>
+        <v>-5.086500000000001</v>
       </c>
       <c r="T27" t="n">
-        <v>-5.9884</v>
+        <v>-5.9953</v>
       </c>
       <c r="U27" t="n">
-        <v>0.9225000000000001</v>
+        <v>0.9090999999999999</v>
       </c>
       <c r="V27" t="n">
-        <v>-9.287800000000001</v>
+        <v>-9.2605</v>
       </c>
       <c r="W27" t="n">
-        <v>6.266999999999999</v>
+        <v>6.2361</v>
       </c>
       <c r="X27" t="n">
-        <v>-15.5546</v>
+        <v>-15.4967</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104705_W28.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104705_W28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.3877</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104705_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104705_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104705_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.2983</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104705_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104705_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.1405</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104705_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104705_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104705_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-3.4089</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104705_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.1405</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104705_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104705_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104705_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-6.2362</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.4163</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104705_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104705_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.6424</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104705_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104705_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104705_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104705_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-2.5058</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104705_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.5741</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104705_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104705_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104705_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104705_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>-1.4163</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104705_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-15.4967</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
